--- a/output/pdf_financials_xlsx/CDR.xlsx
+++ b/output/pdf_financials_xlsx/CDR.xlsx
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.147</v>
+        <v>0.125</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1.532</v>
+        <v>1.493</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.484</v>
+        <v>5.316</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>15.985</v>
@@ -3866,19 +3866,19 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>-62.999</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-65.47499999999999</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-70.267</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-77.223</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-79.467</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>-84.58</v>
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-11.85</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.019</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>56.615</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -4852,19 +4852,19 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-4.208</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.284</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.096</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.218</v>
       </c>
     </row>
     <row r="119">
@@ -11414,7 +11414,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E95" s="5" t="n">
         <v>-62.999</v>
       </c>
@@ -13876,7 +13880,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -24562,7 +24570,11 @@
           <t>Exploration and evaluation expense 2</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -24950,7 +24962,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E303" s="5" t="n">
         <v>-11.85</v>
       </c>
@@ -32514,7 +32530,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E420" s="5" t="n">
         <v>0.022</v>
       </c>

--- a/output/pdf_financials_xlsx/CDR.xlsx
+++ b/output/pdf_financials_xlsx/CDR.xlsx
@@ -745,34 +745,34 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.022</v>
+        <v>11.432</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.039</v>
+        <v>13.024</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.168</v>
+        <v>71.474</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>21.148</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>12.174</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>7.237</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>12.676</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>44.458</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>63.263</v>
       </c>
     </row>
     <row r="11">
@@ -782,34 +782,34 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.125</v>
+        <v>-11.285</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1.493</v>
+        <v>-11.492</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.316</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>15.985</v>
+        <v>-5.163</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>10.268</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.768</v>
+        <v>-11.406</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>3.119</v>
+        <v>-4.118</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.552</v>
+        <v>-12.124</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>57.408</v>
+        <v>12.95</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>69.538</v>
+        <v>6.275</v>
       </c>
     </row>
     <row r="12">
@@ -5076,19 +5076,19 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.105</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.308</v>
       </c>
     </row>
     <row r="125">
@@ -5113,19 +5113,19 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.105</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.308</v>
       </c>
     </row>
     <row r="126">
@@ -14644,7 +14644,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -19598,7 +19602,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -21388,7 +21396,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -26468,20 +26480,20 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E327" s="5" t="n">
-        <v>-11.432</v>
+        <v>11.432</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>-13.024</v>
+        <v>13.024</v>
       </c>
       <c r="G327" s="5" t="n">
-        <v>-71.474</v>
+        <v>71.474</v>
       </c>
       <c r="H327" s="5" t="n">
-        <v>-21.148</v>
+        <v>21.148</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -26489,19 +26501,19 @@
         </is>
       </c>
       <c r="J327" s="5" t="n">
-        <v>-12.174</v>
+        <v>12.174</v>
       </c>
       <c r="K327" s="5" t="n">
-        <v>-7.237</v>
+        <v>7.237</v>
       </c>
       <c r="L327" s="5" t="n">
-        <v>-12.676</v>
+        <v>12.676</v>
       </c>
       <c r="M327" s="5" t="n">
-        <v>-44.458</v>
+        <v>44.458</v>
       </c>
       <c r="N327" s="5" t="n">
-        <v>-63.263</v>
+        <v>63.263</v>
       </c>
     </row>
     <row r="328">

--- a/output/pdf_financials_xlsx/CDR.xlsx
+++ b/output/pdf_financials_xlsx/CDR.xlsx
@@ -5162,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0</v>
+        <v>-2.735</v>
       </c>
     </row>
     <row r="127">
@@ -14440,7 +14440,11 @@
           <t>Dividends paid to non-controlling interest 16a</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CDR.xlsx
+++ b/output/pdf_financials_xlsx/CDR.xlsx
@@ -970,18 +970,16 @@
         <v>-3.318</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-11.892</v>
+        <v>-10.089</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-66.66800000000001</v>
+        <v>-63.311</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-14.07</v>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-17.521</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-11.658</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-11.327</v>
@@ -1009,13 +1007,13 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.803</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.357</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>3.451</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1169,7 +1167,7 @@
         <v>-14.07</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-2.412</v>
+        <v>-0.00026</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-11.327</v>
@@ -1206,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-2.412</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1279,10 +1277,8 @@
       <c r="E23" s="3" t="n">
         <v>-14.07</v>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="3" t="n">
+        <v>-11.658</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-11.327</v>
@@ -1481,18 +1477,16 @@
         <v>-4.024</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-12.317</v>
+        <v>-10.514</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-67.441</v>
+        <v>-64.084</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-14.538</v>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-17.989</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-12.124</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-11.437</v>
@@ -1557,18 +1551,16 @@
         <v>-2.48</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-11.325</v>
+        <v>-9.522</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-64.599</v>
+        <v>-61.242</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-14.538</v>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-17.989</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-12.124</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-10.533</v>
@@ -1596,18 +1588,16 @@
         <v>-1687.074829931973</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-739.2297650130548</v>
+        <v>-621.5404699738904</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1177.954048140044</v>
+        <v>-1116.739606126915</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-90.94776352830779</v>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-112.5367532061307</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>-118.0755746007012</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-1371.484375</v>
@@ -1635,18 +1625,16 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
+        <v>-17.87094855783527</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-5.302396108101278</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-19.69636436276468</v>
+      </c>
+      <c r="F31" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -1682,10 +1670,8 @@
       <c r="E32" s="3" t="n">
         <v>-88.02001876759462</v>
       </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F32" s="3" t="n">
+        <v>-113.5372029606545</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>-1474.869791666667</v>
@@ -4143,10 +4129,8 @@
       <c r="E99" s="3" t="n">
         <v>-14.07</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-11.658</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-11.327</v>
@@ -13360,7 +13344,11 @@
           <t>Deferred income tax recovery 23</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -16194,7 +16182,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -16770,7 +16762,11 @@
           <t>Deferred income tax recovery 21</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -21660,7 +21656,11 @@
           <t>Net loss from continuing operations (13,870)</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -23670,7 +23670,11 @@
           <t>Deferred income tax expense (recovery) 16</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -24656,7 +24660,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -25372,7 +25380,11 @@
           <t>Deferred tax expense (recovery) 17</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E309" s="5" t="n">
         <v>1.803</v>
       </c>
@@ -27130,7 +27142,11 @@
           <t>Deferred income tax recovery 23</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -28620,7 +28636,11 @@
           <t>Deferred income tax recovery 21</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -31174,7 +31194,11 @@
           <t>Net loss from continuing operations (13,870)</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -31242,7 +31266,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -31508,7 +31532,11 @@
           <t>Net loss from continuing operations (0.31)</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -31574,7 +31602,11 @@
           <t>Net income (loss) from discontinued operations 0.08</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -32290,7 +32322,11 @@
           <t>Deferred income tax recovery (expense) 16</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -33146,7 +33182,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
